--- a/html/app/vbr_metadata_template.xlsx
+++ b/html/app/vbr_metadata_template.xlsx
@@ -12855,10 +12855,10 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="0" sqref="C2:C1048576" errorTitle="Not in Controlled Vocabulary" error="The value you entered is not in the controlled vocabulary. Contact the HVPCC if additional CV terms are needed.">
       <formula1>'cv'!$B$2:$B$3</formula1>
     </dataValidation>
-    <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="D1" promptTitle="Required [cv]" prompt="Race of the participant.">
+    <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="D1" promptTitle="Required [cv, list]" prompt="Race of the participant.">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="1" sqref="D2:D1048576" errorTitle="Not in Controlled Vocabulary" error="The value you entered is not in the controlled vocabulary. Contact the HVPCC if additional CV terms are needed.">
+    <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="0" sqref="D2:D1048576" errorTitle="Not in Controlled Vocabulary" error="The value you entered is not in the controlled vocabulary. Contact the HVPCC if additional CV terms are needed.">
       <formula1>'cv'!$C$2:$C$9</formula1>
     </dataValidation>
     <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="E1" promptTitle="Required [cv]" prompt="Ethnicity of the participant.">
@@ -12879,10 +12879,10 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="1" sqref="G2:G1048576" errorTitle="Not in Controlled Vocabulary" error="The value you entered is not in the controlled vocabulary. Contact the HVPCC if additional CV terms are needed.">
       <formula1>'cv'!$F$2:$F$197</formula1>
     </dataValidation>
-    <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="H1" promptTitle="Required [cv]" prompt="Country where participant resided during childhood">
+    <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="H1" promptTitle="Required [cv, list]" prompt="Country where participant resided during childhood">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="1" sqref="H2:H1048576" errorTitle="Not in Controlled Vocabulary" error="The value you entered is not in the controlled vocabulary. Contact the HVPCC if additional CV terms are needed.">
+    <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="0" sqref="H2:H1048576" errorTitle="Not in Controlled Vocabulary" error="The value you entered is not in the controlled vocabulary. Contact the HVPCC if additional CV terms are needed.">
       <formula1>'cv'!$G$2:$G$197</formula1>
     </dataValidation>
     <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="I1" promptTitle="Optional [number]" prompt="Age of pregnancy (in weeks) when participant was born.">
@@ -13330,7 +13330,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="1" sqref="N2:N1048576" errorTitle="Not in Controlled Vocabulary" error="The value you entered is not in the controlled vocabulary. Contact the HVPCC if additional CV terms are needed.">
       <formula1>'cv'!$Q$2:$Q$5</formula1>
     </dataValidation>
-    <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="O1" promptTitle="Optional [ontology]" prompt="NCBI Taxonomy IDs of animals that participant has exposure to. Only the ID (e.g. &quot;NCBI:txid9615&quot;) is needed; the rest of the text is ignored/discarded.">
+    <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="O1" promptTitle="Optional [ontology, list]" prompt="NCBI Taxonomy IDs of animals that participant has exposure to. Only the ID (e.g. &quot;NCBI:txid9615&quot;) is needed; the rest of the text is ignored/discarded.">
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="0" sqref="O2:O1048576" errorTitle="Not in Controlled Vocabulary" error="The value you entered is not in the controlled vocabulary. Contact the HVPCC if additional CV terms are needed.">
@@ -13717,7 +13717,7 @@
     <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B1" promptTitle="Optional [ontology]" prompt="The NCBI BioSample ID associated with this library/processed sample, if this sample has been registered with NCBI. Otherwise, leave this field blank.">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="C1" promptTitle="Conditional [uid]" prompt="`event_uid` is required unless `parent_sample_uid` is provided or `sample_type` is &quot;composite_*&quot;.&#10;&#10;A previously defined event_uid at which this sample was collected. This value must be the same for any sampling that occurred at the same event. May be lef…">
+    <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="C1" promptTitle="Conditional [uid]" prompt="`event_uid` is required unless `parent_sample_uid` is provided, `sample_type` is &quot;composite_*&quot;, or `participant_uid` is &quot;mock&quot;.&#10;&#10;A previously defined event_uid at which this sample was collected. This value must be the same for any sampling that occurred…">
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="D1" promptTitle="Required [cv]" prompt="Lab, group, or facility within a grant-level project where the sample was collected and/or processed. This should be the group responsible for metadata about the sample.">

--- a/html/app/vbr_metadata_template.xlsx
+++ b/html/app/vbr_metadata_template.xlsx
@@ -6533,11 +6533,6 @@
           <t xml:space="preserve">  throat [UBERON:0000341]</t>
         </is>
       </c>
-      <c r="AQ45" t="inlineStr">
-        <is>
-          <t>unavailable</t>
-        </is>
-      </c>
       <c r="BJ45" t="inlineStr">
         <is>
           <t>PacBio RS II</t>
@@ -12086,11 +12081,6 @@
       <c r="Z180" t="inlineStr">
         <is>
           <t>Semaglutide / Rybelsus [DB13928:oral]</t>
-        </is>
-      </c>
-      <c r="AP180" t="inlineStr">
-        <is>
-          <t>unavailable</t>
         </is>
       </c>
     </row>
@@ -13753,17 +13743,17 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="0" sqref="J2:J1048576" errorTitle="Not in Controlled Vocabulary" error="The value you entered is not in the controlled vocabulary. Contact the HVPCC if additional CV terms are needed.">
       <formula1>'cv'!$AO$2:$AO$2</formula1>
     </dataValidation>
-    <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="K1" promptTitle="Conditional [ontology]" prompt="At least one of `anatomical_site` or `body_product` must be provided (other than &quot;unavailable&quot;).&#10;&#10;Uberon Ontology ID or Cell Ontology ID for the anatomical structure from which sample was obtained. Use the most specific term that applies to your data fro…">
+    <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="K1" promptTitle="Conditional [ontology]" prompt="At least one of `anatomical_site` or `body_product` must be provided.&#10;&#10;Uberon Ontology ID or Cell Ontology ID for the anatomical structure from which sample was obtained. Use the most specific term that applies to your data from the Uberon ontology &quot;anat…">
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="0" sqref="K2:K1048576" errorTitle="Not in Controlled Vocabulary" error="The value you entered is not in the controlled vocabulary. Contact the HVPCC if additional CV terms are needed.">
-      <formula1>'cv'!$AP$2:$AP$180</formula1>
-    </dataValidation>
-    <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="L1" promptTitle="Conditional [ontology]" prompt="At least one of `anatomical_site` or `body_product` must be provided (other than &quot;unavailable&quot;).&#10;&#10;Uberon ontology ID for the substance collected from the participant, e.g. stool, mucus, urine. Use any term from the Uberon ontology &quot;organism substance&quot; br…">
+      <formula1>'cv'!$AP$2:$AP$179</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="L1" promptTitle="Conditional [ontology]" prompt="At least one of `anatomical_site` or `body_product` must be provided.&#10;&#10;Uberon ontology ID for the substance collected from the participant, e.g. stool, mucus, urine. Use any term from the Uberon ontology &quot;organism substance&quot; branch. Only the ID (e.g. &quot;UB…">
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="0" sqref="L2:L1048576" errorTitle="Not in Controlled Vocabulary" error="The value you entered is not in the controlled vocabulary. Contact the HVPCC if additional CV terms are needed.">
-      <formula1>'cv'!$AQ$2:$AQ$45</formula1>
+      <formula1>'cv'!$AQ$2:$AQ$44</formula1>
     </dataValidation>
     <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="M1" promptTitle="Required [ontology]" prompt="NCIT ID for the method used to collect the sample. Use any terms from the &quot;biospecimen collection method&quot; or &quot;diagnostic procedure&quot; branches in NCIT. If you have difficulty finding a term in NCIT that corresponds to your method, contact the HVPCC. Only t…">
       <formula1>0</formula1>

--- a/html/app/vbr_metadata_template.xlsx
+++ b/html/app/vbr_metadata_template.xlsx
@@ -8,7 +8,7 @@
   <sheets>
     <sheet name="cv" sheetId="1" state="hidden" r:id="rId1"/>
     <sheet name="participants" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="events" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="participant_event_attributes" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="samples" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="libraries" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="analyses" sheetId="6" state="visible" r:id="rId6"/>
@@ -2482,11 +2482,6 @@
           <t>WCS</t>
         </is>
       </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>VIRAL RNA</t>
-        </is>
-      </c>
       <c r="BG7" t="inlineStr">
         <is>
           <t>MF</t>
@@ -2704,11 +2699,6 @@
           <t>CLONE</t>
         </is>
       </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>GENOMIC SINGLE CELL</t>
-        </is>
-      </c>
       <c r="BG8" t="inlineStr">
         <is>
           <t>CF-S</t>
@@ -2881,11 +2871,6 @@
           <t>POOLCLONE</t>
         </is>
       </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>TRANSCRIPTOMIC SINGLE CELL</t>
-        </is>
-      </c>
       <c r="BG9" t="inlineStr">
         <is>
           <t>CF-M</t>
@@ -3038,11 +3023,6 @@
           <t>AMPLICON</t>
         </is>
       </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
       <c r="BG10" t="inlineStr">
         <is>
           <t>CF-H</t>
@@ -3436,7 +3416,7 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>glmc</t>
+          <t>gilber</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
@@ -3466,7 +3446,7 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>glmc</t>
+          <t>gilber</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -3573,7 +3553,7 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>lareau</t>
+          <t>glmc</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
@@ -3598,7 +3578,7 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>lareau</t>
+          <t>glmc</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -3705,7 +3685,7 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>li</t>
+          <t>ismagilov</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
@@ -3730,7 +3710,7 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>li</t>
+          <t>ismagilov</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -3832,7 +3812,7 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>mason</t>
+          <t>lareau</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
@@ -3857,7 +3837,7 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>mason</t>
+          <t>lareau</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -3959,7 +3939,7 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>moustafa</t>
+          <t>li</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
@@ -3984,7 +3964,7 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>moustafa</t>
+          <t>li</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -4086,7 +4066,7 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>naik</t>
+          <t>mason</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
@@ -4111,7 +4091,7 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>naik</t>
+          <t>mason</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -4208,7 +4188,7 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>sabeti</t>
+          <t>moustafa</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
@@ -4233,7 +4213,7 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>sabeti</t>
+          <t>moustafa</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -4330,7 +4310,7 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>snyder</t>
+          <t>naik</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
@@ -4355,7 +4335,7 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>snyder</t>
+          <t>naik</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -4442,7 +4422,7 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>tcgb</t>
+          <t>sabeti</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
@@ -4467,7 +4447,7 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>tcgb</t>
+          <t>sabeti</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -4554,7 +4534,7 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>yracheta</t>
+          <t>snyder</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
@@ -4579,7 +4559,7 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>yracheta</t>
+          <t>snyder</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -4666,7 +4646,7 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>zhou</t>
+          <t>tcgb</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
@@ -4691,7 +4671,7 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>zhou</t>
+          <t>tcgb</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -4776,6 +4756,11 @@
           <t>PCV20 (20-valent Pneumococcal conjugate) [CVX:216]</t>
         </is>
       </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>thoreen</t>
+        </is>
+      </c>
       <c r="AP24" t="inlineStr">
         <is>
           <t xml:space="preserve">  bronchiole [UBERON:0002186]</t>
@@ -4789,6 +4774,11 @@
       <c r="AS24" t="inlineStr">
         <is>
           <t xml:space="preserve">  Sputum specimen container [SNOMED:702223006]</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>thoreen</t>
         </is>
       </c>
       <c r="BE24" t="inlineStr">
@@ -4873,6 +4863,11 @@
           <t>Pneumococcal vaccine (Unspecified formulation) [CVX:109]</t>
         </is>
       </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>yracheta</t>
+        </is>
+      </c>
       <c r="AP25" t="inlineStr">
         <is>
           <t xml:space="preserve">  terminal bronchiole [UBERON:0002187]</t>
@@ -4886,6 +4881,11 @@
       <c r="AS25" t="inlineStr">
         <is>
           <t xml:space="preserve">  Fecal specimen container [SNOMED:706047007]</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>yracheta</t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
@@ -4970,6 +4970,11 @@
           <t>Rotavirus vaccine (Pentavalent) [CVX:116]</t>
         </is>
       </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>zhou</t>
+        </is>
+      </c>
       <c r="AP26" t="inlineStr">
         <is>
           <t xml:space="preserve">  respiratory bronchiole [UBERON:0002188]</t>
@@ -4983,6 +4988,11 @@
       <c r="AS26" t="inlineStr">
         <is>
           <t xml:space="preserve">  Urine bottle [SNOMED:360005000]</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>zhou</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
@@ -13245,7 +13255,7 @@
     <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="A1" promptTitle="Required [uid]" prompt="A previously defined participant_uid for which this event information was gathered.">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B1" promptTitle="Required [uid]" prompt="HVP-unique event identifier. See VBR website for UID format.">
+    <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B1" promptTitle="Required [uid]" prompt="Event at which participant was assayed. This value must be the same for any sampling that occured at the same event.">
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="C1" promptTitle="Required [number]" prompt="Participant's age at time of sample collection. When age is unavailable or 90+ years, enter &quot;unavailable&quot; and complete the `age_range` field.">
@@ -13529,9 +13539,9 @@
   <cols>
     <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" style="1" width="13.609"/>
     <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" style="1" width="15.207"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" style="1" width="12.082"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" style="1" width="6.312"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" style="1" width="16.641"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" style="1" width="16.641"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" style="1" width="12.082"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" style="1" width="6.312"/>
     <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" style="1" width="14.609"/>
     <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" style="1" width="17.805"/>
     <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" style="1" width="20.105"/>
@@ -13568,19 +13578,19 @@
           <t>biosample_id</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>participant_uid</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>event_uid</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>lab</t>
-        </is>
-      </c>
-      <c r="E1" s="5" t="inlineStr">
-        <is>
-          <t>participant_uid</t>
         </is>
       </c>
       <c r="F1" s="5" t="inlineStr">
@@ -13707,17 +13717,17 @@
     <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B1" promptTitle="Optional [ontology]" prompt="The NCBI BioSample ID associated with this library/processed sample, if this sample has been registered with NCBI. Otherwise, leave this field blank.">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="C1" promptTitle="Conditional [uid]" prompt="`event_uid` is required unless `parent_sample_uid` is provided, `sample_type` is &quot;composite_*&quot;, or `participant_uid` is &quot;mock&quot;.&#10;&#10;A previously defined event_uid at which this sample was collected. This value must be the same for any sampling that occurred…">
+    <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="C1" promptTitle="Required [uid, list]" prompt="Identifier of the participant (s) from which the sample came. Participant id must be unique within a project. This participant id should have associated metadata from the Participant Metadata dictionary. For composite samples, indicate identifers of all …">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="D1" promptTitle="Required [cv]" prompt="Lab, group, or facility within a grant-level project where the sample was collected and/or processed. This should be the group responsible for metadata about the sample.">
+    <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="D1" promptTitle="Conditional [uid]" prompt="`event_uid` is required unless `parent_sample_uid` is provided, `sample_type` is &quot;composite_*&quot;, or `participant_uid` is &quot;mock&quot;.&#10;&#10;A previously defined event_uid at which this sample was collected. This value must be the same for any sampling that occurred…">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="1" sqref="D2:D1048576" errorTitle="Not in Controlled Vocabulary" error="The value you entered is not in the controlled vocabulary. Contact the HVPCC if additional CV terms are needed.">
-      <formula1>'cv'!$AL$2:$AL$23</formula1>
-    </dataValidation>
-    <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="E1" promptTitle="Required [uid, list]" prompt="Identifier of the participant (s) from which the sample came. Participant id must be unique within a project. This participant id should have associated metadata from the Participant Metadata dictionary. For composite samples, indicate identifers of all …">
+    <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="E1" promptTitle="Required [cv]" prompt="Lab, group, or facility within a grant-level project where the sample was collected and/or processed. This should be the group responsible for metadata about the sample.">
       <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="1" sqref="E2:E1048576" errorTitle="Not in Controlled Vocabulary" error="The value you entered is not in the controlled vocabulary. Contact the HVPCC if additional CV terms are needed.">
+      <formula1>'cv'!$AL$2:$AL$26</formula1>
     </dataValidation>
     <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="F1" promptTitle="Required [cv]" prompt="Indicates the composition of the sample - describes if the sample comes from one participant or is a mixture of material from more than one participant. This field can also include terms for various in vitro or cell culture systems. Contact the HVPCC if …">
       <formula1>0</formula1>
@@ -13986,7 +13996,7 @@
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="1" sqref="C2:C1048576" errorTitle="Not in Controlled Vocabulary" error="The value you entered is not in the controlled vocabulary. Contact the HVPCC if additional CV terms are needed.">
-      <formula1>'cv'!$AZ$2:$AZ$23</formula1>
+      <formula1>'cv'!$AZ$2:$AZ$26</formula1>
     </dataValidation>
     <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="D1" promptTitle="Required [yes/no]" prompt="Is this an aliquot, or subsample, of the original library or processed sample?">
       <formula1>0</formula1>
@@ -13997,7 +14007,7 @@
     <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="E1" promptTitle="Conditional [uid]" prompt="`parent_library_uid` is required when `library_aliquot` is &quot;yes&quot;.&#10;&#10;The identifier of the library/processed sample from which a library/processed sample is built or from which an aliquot was taken. Only applicable if `library_aliquot` is &quot;yes&quot;.">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="F1" promptTitle="Required" prompt="This is a free text field. Please use the suggested terms below. If none of these terms work, you may use a new term but please notify the HVPCC of the new term(s) added. Please keep the terms general, and exclud version details.">
+    <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="F1" promptTitle="Required" prompt="Technique performed to create the library/processed sample. This is a free text field. Please use the suggested root terms below, and add on a version or more specific details. If none of these terms work, you may use a new root term but please notify th…">
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="0" sqref="F2:F1048576" errorTitle="Not in Controlled Vocabulary" error="The value you entered is not in the controlled vocabulary. Contact the HVPCC if additional CV terms are needed.">
@@ -14050,7 +14060,7 @@
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="1" sqref="O2:O1048576" errorTitle="Not in Controlled Vocabulary" error="The value you entered is not in the controlled vocabulary. Contact the HVPCC if additional CV terms are needed.">
-      <formula1>'cv'!$BF$2:$BF$10</formula1>
+      <formula1>'cv'!$BF$2:$BF$6</formula1>
     </dataValidation>
     <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="P1" promptTitle="Conditional [cv]" prompt="Required for sequence data.&#10;&#10;The method used to get the nucleic acid sample that will be sequenced, for example RANDOM (random shearing of nucleic acid), PolyA (selection of mRNAs based on binding to polyA tails).">
       <formula1>0</formula1>

--- a/html/app/vbr_metadata_template.xlsx
+++ b/html/app/vbr_metadata_template.xlsx
@@ -2202,7 +2202,7 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oral Cocktail </t>
+          <t>Oral Cocktail</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t xml:space="preserve">VTM </t>
+          <t>VTM</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>gilber</t>
+          <t>glmc</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>gilber</t>
+          <t>glmc</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>glmc</t>
+          <t>lareau</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
@@ -3578,7 +3578,7 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>glmc</t>
+          <t>lareau</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>ismagilov</t>
+          <t>li</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>ismagilov</t>
+          <t>li</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>lareau</t>
+          <t>mason</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>lareau</t>
+          <t>mason</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>li</t>
+          <t>moustafa</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
@@ -3964,7 +3964,7 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>li</t>
+          <t>moustafa</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>mason</t>
+          <t>naik</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>mason</t>
+          <t>naik</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>moustafa</t>
+          <t>sabeti</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>moustafa</t>
+          <t>sabeti</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>naik</t>
+          <t>snyder</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>naik</t>
+          <t>snyder</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -4422,7 +4422,7 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>sabeti</t>
+          <t>tcgb</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>sabeti</t>
+          <t>tcgb</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>snyder</t>
+          <t>yracheta</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>snyder</t>
+          <t>yracheta</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>tcgb</t>
+          <t>zhou</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>tcgb</t>
+          <t>zhou</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -4756,11 +4756,6 @@
           <t>PCV20 (20-valent Pneumococcal conjugate) [CVX:216]</t>
         </is>
       </c>
-      <c r="AL24" t="inlineStr">
-        <is>
-          <t>thoreen</t>
-        </is>
-      </c>
       <c r="AP24" t="inlineStr">
         <is>
           <t xml:space="preserve">  bronchiole [UBERON:0002186]</t>
@@ -4774,11 +4769,6 @@
       <c r="AS24" t="inlineStr">
         <is>
           <t xml:space="preserve">  Sputum specimen container [SNOMED:702223006]</t>
-        </is>
-      </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>thoreen</t>
         </is>
       </c>
       <c r="BE24" t="inlineStr">
@@ -4863,11 +4853,6 @@
           <t>Pneumococcal vaccine (Unspecified formulation) [CVX:109]</t>
         </is>
       </c>
-      <c r="AL25" t="inlineStr">
-        <is>
-          <t>yracheta</t>
-        </is>
-      </c>
       <c r="AP25" t="inlineStr">
         <is>
           <t xml:space="preserve">  terminal bronchiole [UBERON:0002187]</t>
@@ -4881,11 +4866,6 @@
       <c r="AS25" t="inlineStr">
         <is>
           <t xml:space="preserve">  Fecal specimen container [SNOMED:706047007]</t>
-        </is>
-      </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>yracheta</t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
@@ -4970,11 +4950,6 @@
           <t>Rotavirus vaccine (Pentavalent) [CVX:116]</t>
         </is>
       </c>
-      <c r="AL26" t="inlineStr">
-        <is>
-          <t>zhou</t>
-        </is>
-      </c>
       <c r="AP26" t="inlineStr">
         <is>
           <t xml:space="preserve">  respiratory bronchiole [UBERON:0002188]</t>
@@ -4988,11 +4963,6 @@
       <c r="AS26" t="inlineStr">
         <is>
           <t xml:space="preserve">  Urine bottle [SNOMED:360005000]</t>
-        </is>
-      </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>zhou</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
@@ -11913,12 +11883,12 @@
     <row r="174">
       <c r="F174" t="inlineStr">
         <is>
-          <t>Tajikistan</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Tajikistan</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="T174" t="inlineStr">
@@ -11940,12 +11910,12 @@
     <row r="175">
       <c r="F175" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Tajikistan</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Tajikistan</t>
         </is>
       </c>
       <c r="T175" t="inlineStr">
@@ -11967,12 +11937,12 @@
     <row r="176">
       <c r="F176" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="T176" t="inlineStr">
@@ -11994,12 +11964,12 @@
     <row r="177">
       <c r="F177" t="inlineStr">
         <is>
-          <t>Timor-Leste</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Timor-Leste</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="T177" t="inlineStr">
@@ -12021,12 +11991,12 @@
     <row r="178">
       <c r="F178" t="inlineStr">
         <is>
-          <t>Togo</t>
+          <t>Timor-Leste</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Togo</t>
+          <t>Timor-Leste</t>
         </is>
       </c>
       <c r="T178" t="inlineStr">
@@ -12048,12 +12018,12 @@
     <row r="179">
       <c r="F179" t="inlineStr">
         <is>
-          <t>Tonga</t>
+          <t>Togo</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Tonga</t>
+          <t>Togo</t>
         </is>
       </c>
       <c r="T179" t="inlineStr">
@@ -12075,12 +12045,12 @@
     <row r="180">
       <c r="F180" t="inlineStr">
         <is>
-          <t>Trinidad and Tobago</t>
+          <t>Tonga</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Trinidad and Tobago</t>
+          <t>Tonga</t>
         </is>
       </c>
       <c r="T180" t="inlineStr">
@@ -12097,12 +12067,12 @@
     <row r="181">
       <c r="F181" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Trinidad and Tobago</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Trinidad and Tobago</t>
         </is>
       </c>
       <c r="T181" t="inlineStr">
@@ -12119,12 +12089,12 @@
     <row r="182">
       <c r="F182" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="T182" t="inlineStr">
@@ -12141,12 +12111,12 @@
     <row r="183">
       <c r="F183" t="inlineStr">
         <is>
-          <t>Turkmenistan</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Turkmenistan</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="T183" t="inlineStr">
@@ -12163,12 +12133,12 @@
     <row r="184">
       <c r="F184" t="inlineStr">
         <is>
-          <t>Tuvalu</t>
+          <t>Turkmenistan</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Tuvalu</t>
+          <t>Turkmenistan</t>
         </is>
       </c>
       <c r="T184" t="inlineStr">
@@ -12185,12 +12155,12 @@
     <row r="185">
       <c r="F185" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Tuvalu</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Tuvalu</t>
         </is>
       </c>
       <c r="T185" t="inlineStr">
@@ -12207,12 +12177,12 @@
     <row r="186">
       <c r="F186" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="T186" t="inlineStr">
@@ -12229,12 +12199,12 @@
     <row r="187">
       <c r="F187" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="T187" t="inlineStr">
@@ -12251,12 +12221,12 @@
     <row r="188">
       <c r="F188" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="T188" t="inlineStr">
@@ -12273,12 +12243,12 @@
     <row r="189">
       <c r="F189" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="T189" t="inlineStr">
@@ -12295,12 +12265,12 @@
     <row r="190">
       <c r="F190" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="T190" t="inlineStr">
@@ -12317,12 +12287,12 @@
     <row r="191">
       <c r="F191" t="inlineStr">
         <is>
-          <t>Vanuatu</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Vanuatu</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="T191" t="inlineStr">
@@ -12339,12 +12309,12 @@
     <row r="192">
       <c r="F192" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Vanuatu</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Vanuatu</t>
         </is>
       </c>
       <c r="T192" t="inlineStr">
@@ -12361,12 +12331,12 @@
     <row r="193">
       <c r="F193" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="T193" t="inlineStr">
@@ -12383,12 +12353,12 @@
     <row r="194">
       <c r="F194" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="T194" t="inlineStr">
@@ -12405,12 +12375,12 @@
     <row r="195">
       <c r="F195" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="T195" t="inlineStr">
@@ -12427,12 +12397,12 @@
     <row r="196">
       <c r="F196" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="T196" t="inlineStr">
@@ -12449,26 +12419,36 @@
     <row r="197">
       <c r="F197" t="inlineStr">
         <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>FARMING, FISHING &amp; FORESTRY [SNOMED:159812002]</t>
+        </is>
+      </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>Timolol / Timoptic [DB00373:ophthalmic]</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="F198" t="inlineStr">
+        <is>
           <t>unavailable</t>
         </is>
       </c>
-      <c r="G197" t="inlineStr">
+      <c r="G198" t="inlineStr">
         <is>
           <t>unavailable</t>
         </is>
       </c>
-      <c r="T197" t="inlineStr">
-        <is>
-          <t>FARMING, FISHING &amp; FORESTRY [SNOMED:159812002]</t>
-        </is>
-      </c>
-      <c r="Z197" t="inlineStr">
-        <is>
-          <t>Timolol / Timoptic [DB00373:ophthalmic]</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
       <c r="T198" t="inlineStr">
         <is>
           <t xml:space="preserve">  Farmer / Rancher [SNOMED:106388008]</t>
@@ -12877,13 +12857,13 @@
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="1" sqref="G2:G1048576" errorTitle="Not in Controlled Vocabulary" error="The value you entered is not in the controlled vocabulary. Contact the HVPCC if additional CV terms are needed.">
-      <formula1>'cv'!$F$2:$F$197</formula1>
+      <formula1>'cv'!$F$2:$F$198</formula1>
     </dataValidation>
     <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="H1" promptTitle="Required [cv, list]" prompt="Country where participant resided during childhood">
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="0" sqref="H2:H1048576" errorTitle="Not in Controlled Vocabulary" error="The value you entered is not in the controlled vocabulary. Contact the HVPCC if additional CV terms are needed.">
-      <formula1>'cv'!$G$2:$G$197</formula1>
+      <formula1>'cv'!$G$2:$G$198</formula1>
     </dataValidation>
     <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="I1" promptTitle="Optional [number]" prompt="Age of pregnancy (in weeks) when participant was born.">
       <formula1>0</formula1>
@@ -13727,7 +13707,7 @@
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="1" sqref="E2:E1048576" errorTitle="Not in Controlled Vocabulary" error="The value you entered is not in the controlled vocabulary. Contact the HVPCC if additional CV terms are needed.">
-      <formula1>'cv'!$AL$2:$AL$26</formula1>
+      <formula1>'cv'!$AL$2:$AL$23</formula1>
     </dataValidation>
     <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="F1" promptTitle="Required [cv]" prompt="Indicates the composition of the sample - describes if the sample comes from one participant or is a mixture of material from more than one participant. This field can also include terms for various in vitro or cell culture systems. Contact the HVPCC if …">
       <formula1>0</formula1>
@@ -13989,14 +13969,14 @@
     <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="A1" promptTitle="Required [uid]" prompt="HVP-unique sequencing library or processed sample identifier. See VBR website for UID format.">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B1" promptTitle="Required [uid]" prompt="A previously defined sample_uid from which the library or processed sample was derived. ">
+    <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B1" promptTitle="Required [uid]" prompt="A previously defined sample_uid from which the library or processed sample was derived.">
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="C1" promptTitle="Required [cv]" prompt="The lab that performed the library preparation protocol on the sample.">
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="1" sqref="C2:C1048576" errorTitle="Not in Controlled Vocabulary" error="The value you entered is not in the controlled vocabulary. Contact the HVPCC if additional CV terms are needed.">
-      <formula1>'cv'!$AZ$2:$AZ$26</formula1>
+      <formula1>'cv'!$AZ$2:$AZ$23</formula1>
     </dataValidation>
     <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="D1" promptTitle="Required [yes/no]" prompt="Is this an aliquot, or subsample, of the original library or processed sample?">
       <formula1>0</formula1>
@@ -14170,7 +14150,7 @@
     <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="F1" promptTitle="Optional" prompt="A stable, permanent url where documentation on the details of the analysis and how it was performed can be found. The description must be detailed enough that others can reproduce the process. Suggested locations for this information include, but are not…">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="G1" promptTitle="Optional" prompt="If a community workspace or compute infrastructure (such as Terra or CyVerse) was used for the analysis, put the name of the workspace or infrastructure here. ">
+    <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="G1" promptTitle="Optional" prompt="If a community workspace or compute infrastructure (such as Terra or CyVerse) was used for the analysis, put the name of the workspace or infrastructure here.">
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="H1" promptTitle="Optional" prompt="If a containerized version of the pipeline was used, the url of where that container can be found.">
@@ -14281,7 +14261,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="0" sqref="D2:D1048576" errorTitle="Not in Controlled Vocabulary" error="The value you entered is not in the controlled vocabulary. Contact the HVPCC if additional CV terms are needed.">
       <formula1>'cv'!$BK$2:$BK$19</formula1>
     </dataValidation>
-    <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="E1" promptTitle="Required [cv]" prompt="Term that indicates the type of data contained in the file. Counts should only be used for summary information from a single sample. If fastq files are demultiplexed, please use demultiplexed_fastq. ">
+    <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="E1" promptTitle="Required [cv]" prompt="Term that indicates the type of data contained in the file. Counts should only be used for summary information from a single sample. If fastq files are demultiplexed, please use demultiplexed_fastq.">
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="1" sqref="E2:E1048576" errorTitle="Not in Controlled Vocabulary" error="The value you entered is not in the controlled vocabulary. Contact the HVPCC if additional CV terms are needed.">

--- a/html/app/vbr_metadata_template.xlsx
+++ b/html/app/vbr_metadata_template.xlsx
@@ -2202,7 +2202,7 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>Oral Cocktail</t>
+          <t xml:space="preserve">Oral Cocktail </t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>VTM</t>
+          <t xml:space="preserve">VTM </t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>EDTA</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
@@ -3576,6 +3576,11 @@
           <t>TISSUE BIOPSY &amp; SURGICAL INSTRUMENTS</t>
         </is>
       </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>Elution Buffer (AVE)</t>
+        </is>
+      </c>
       <c r="AZ14" t="inlineStr">
         <is>
           <t>lareau</t>
@@ -3708,6 +3713,11 @@
           <t xml:space="preserve">  Biopsy needle, device [SNOMED:118377000]</t>
         </is>
       </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>Distilled water</t>
+        </is>
+      </c>
       <c r="AZ15" t="inlineStr">
         <is>
           <t>li</t>
@@ -3833,6 +3843,11 @@
       <c r="AS16" t="inlineStr">
         <is>
           <t xml:space="preserve">  Biopsy punch [SNOMED:466467006]</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>unavailable</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
@@ -13235,7 +13250,7 @@
     <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="A1" promptTitle="Required [uid]" prompt="A previously defined participant_uid for which this event information was gathered.">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B1" promptTitle="Required [uid]" prompt="Event at which participant was assayed. This value must be the same for any sampling that occured at the same event.">
+    <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B1" promptTitle="Required [uid]" prompt="A sampling event at which subject was assayed. This value must be the same for any sampling that occured at the same event. Each study is expected to have a small set of unique event_uid values that can be reused across participants for corresponding sam…">
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="C1" promptTitle="Required [number]" prompt="Participant's age at time of sample collection. When age is unavailable or 90+ years, enter &quot;unavailable&quot; and complete the `age_range` field.">
@@ -13775,11 +13790,11 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="1" sqref="R2:R1048576" errorTitle="Not in Controlled Vocabulary" error="The value you entered is not in the controlled vocabulary. Contact the HVPCC if additional CV terms are needed.">
       <formula1>'cv'!$AU$2:$AU$7</formula1>
     </dataValidation>
-    <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="S1" promptTitle="Required [cv]" prompt="Additive/preservative in which sample is stored or initially stored.">
+    <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="S1" promptTitle="Required [cv, list]" prompt="Additive/preservative in which sample is stored or initially stored.">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="1" sqref="S2:S1048576" errorTitle="Not in Controlled Vocabulary" error="The value you entered is not in the controlled vocabulary. Contact the HVPCC if additional CV terms are needed.">
-      <formula1>'cv'!$AV$2:$AV$13</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="0" sqref="S2:S1048576" errorTitle="Not in Controlled Vocabulary" error="The value you entered is not in the controlled vocabulary. Contact the HVPCC if additional CV terms are needed.">
+      <formula1>'cv'!$AV$2:$AV$16</formula1>
     </dataValidation>
     <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="T1" promptTitle="Optional [uid, list]" prompt="Sample identifier of linked control. This can be a semicolon separated list, if there are multiple controls associated with the sample. This field is to be populated only for experimental samples, not for control samples. The purpose of this field is to …">
       <formula1>0</formula1>

--- a/html/app/vbr_metadata_template.xlsx
+++ b/html/app/vbr_metadata_template.xlsx
@@ -3553,7 +3553,7 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>lareau</t>
+          <t>kapila</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>lareau</t>
+          <t>kapila</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>li</t>
+          <t>lareau</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>li</t>
+          <t>lareau</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>mason</t>
+          <t>li</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>mason</t>
+          <t>li</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>moustafa</t>
+          <t>mason</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>moustafa</t>
+          <t>mason</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>naik</t>
+          <t>moustafa</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>naik</t>
+          <t>moustafa</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>sabeti</t>
+          <t>naik</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>sabeti</t>
+          <t>naik</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>snyder</t>
+          <t>sabeti</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>snyder</t>
+          <t>sabeti</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>tcgb</t>
+          <t>snyder</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>tcgb</t>
+          <t>snyder</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>yracheta</t>
+          <t>tcgb</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>yracheta</t>
+          <t>tcgb</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>zhou</t>
+          <t>yracheta</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>zhou</t>
+          <t>yracheta</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -4771,6 +4771,11 @@
           <t>PCV20 (20-valent Pneumococcal conjugate) [CVX:216]</t>
         </is>
       </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>zhou</t>
+        </is>
+      </c>
       <c r="AP24" t="inlineStr">
         <is>
           <t xml:space="preserve">  bronchiole [UBERON:0002186]</t>
@@ -4784,6 +4789,11 @@
       <c r="AS24" t="inlineStr">
         <is>
           <t xml:space="preserve">  Sputum specimen container [SNOMED:702223006]</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>zhou</t>
         </is>
       </c>
       <c r="BE24" t="inlineStr">
@@ -13722,7 +13732,7 @@
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="1" sqref="E2:E1048576" errorTitle="Not in Controlled Vocabulary" error="The value you entered is not in the controlled vocabulary. Contact the HVPCC if additional CV terms are needed.">
-      <formula1>'cv'!$AL$2:$AL$23</formula1>
+      <formula1>'cv'!$AL$2:$AL$24</formula1>
     </dataValidation>
     <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="F1" promptTitle="Required [cv]" prompt="Indicates the composition of the sample - describes if the sample comes from one participant or is a mixture of material from more than one participant. This field can also include terms for various in vitro or cell culture systems. Contact the HVPCC if …">
       <formula1>0</formula1>
@@ -13991,7 +14001,7 @@
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="1" sqref="C2:C1048576" errorTitle="Not in Controlled Vocabulary" error="The value you entered is not in the controlled vocabulary. Contact the HVPCC if additional CV terms are needed.">
-      <formula1>'cv'!$AZ$2:$AZ$23</formula1>
+      <formula1>'cv'!$AZ$2:$AZ$24</formula1>
     </dataValidation>
     <dataValidation type="textLength" operator="greaterThan" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="D1" promptTitle="Required [yes/no]" prompt="Is this an aliquot, or subsample, of the original library or processed sample?">
       <formula1>0</formula1>
